--- a/TAU5 - Student Group List V0.1 (13.01.2026).xlsx
+++ b/TAU5 - Student Group List V0.1 (13.01.2026).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\OneDrive\Desktop\Work\DMS Tau5\dms_demo_tau5\frontend\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Desktop\CH_FILES\Development\dms_demo_tau5\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DA77D4-1AA3-4A56-B7B7-7B575CB06E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ED0C77-B8D2-4F96-9FFA-81467471DB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28215" yWindow="3015" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group Students" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Asset Types</t>
   </si>
@@ -80,12 +80,45 @@
   <si>
     <t>Company</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ComplianceHub</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Group Students List</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,8 +152,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +186,16 @@
         <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
+    </fill>
+    <fill>
+      <gradientFill>
+        <stop position="0">
+          <color theme="1"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF002060"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
   <borders count="3">
@@ -190,7 +254,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -214,155 +278,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>712470</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9828CB6D-17CF-4840-A00B-00432902B5BE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="104775"/>
-          <a:ext cx="8896350" cy="712470"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:gradFill flip="none" rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1"/>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:srgbClr val="002060"/>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="0" scaled="1"/>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>ComplianceHub</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Group Students List</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="1">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>149072</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>87630</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>589400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>592455</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23B033B5-E670-414A-B2B9-EF869DEDB40F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="358622" y="182880"/>
-          <a:ext cx="451758" cy="510540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -631,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G4616"/>
+  <dimension ref="B1:K4616"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="3" customWidth="1"/>
@@ -646,7 +561,9 @@
   <sheetData>
     <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:7" ht="53.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -37581,7 +37498,6 @@
     <oddHeader>&amp;A</oddHeader>
     <oddFooter>&amp;L&amp;B Confidential&amp;B&amp;C&amp;D&amp;RPage &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
